--- a/Tools/Luban/DataTables/Datas/Y_音效.xlsx
+++ b/Tools/Luban/DataTables/Datas/Y_音效.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16725"/>
+    <workbookView windowHeight="17055"/>
   </bookViews>
   <sheets>
     <sheet name="temp" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="145">
   <si>
     <t>##var</t>
   </si>
@@ -56,6 +56,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>(list#sep=,),string</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -182,283 +185,283 @@
     <t>绵羊NPC叫声</t>
   </si>
   <si>
+    <t>Sounds/NPCSound/Sheep_Bleat_1,Sounds/NPCSound/Sheep_Bleat_2,Sounds/NPCSound/Sheep_Bleat_3,Sounds/NPCSound/Sheep_Bleat_4</t>
+  </si>
+  <si>
+    <t>Q_Bouncy_Crop_1</t>
+  </si>
+  <si>
+    <t>q弹作物1（蘑菇碰撞时）</t>
+  </si>
+  <si>
+    <t>Sounds/PlantsSound/Q_Bouncy_Crop_1,Sounds/PlantsSound/Q_Bouncy_Crop_2,Sounds/PlantsSound/Q_Bouncy_Crop_3</t>
+  </si>
+  <si>
+    <t>Character_Planting_Plant</t>
+  </si>
+  <si>
+    <t>人物种下植物</t>
+  </si>
+  <si>
+    <t>Sounds/PlantsSound/Character_Planting_Plant</t>
+  </si>
+  <si>
+    <t>Crop_Falling_to_Ground</t>
+  </si>
+  <si>
+    <t>作物落地</t>
+  </si>
+  <si>
+    <t>Sounds/PlantsSound/Crop_Falling_to_Ground</t>
+  </si>
+  <si>
+    <t>Bowling_Pin_Falling_Sound</t>
+  </si>
+  <si>
+    <t>保龄球倒地声音（胡萝卜被碰）</t>
+  </si>
+  <si>
+    <t>Sounds/PlantsSound/Bowling_Pin_Falling_Sound</t>
+  </si>
+  <si>
+    <t>Bowling_Ball_Rolling_Sound</t>
+  </si>
+  <si>
+    <t>保龄球滚动声音（猕猴桃状态玩家移动）</t>
+  </si>
+  <si>
+    <t>Sounds/PlantsSound/Bowling_Ball_Rolling_Sound</t>
+  </si>
+  <si>
+    <t>Bowling_Ball_Collision_Sound</t>
+  </si>
+  <si>
+    <t>保龄球碰撞声音（猕猴桃碰撞）</t>
+  </si>
+  <si>
+    <t>Sounds/PlantsSound/Bowling_Ball_Collision_Sound</t>
+  </si>
+  <si>
+    <t>Pumpkin_Swallowing</t>
+  </si>
+  <si>
+    <t>南瓜吞咽</t>
+  </si>
+  <si>
+    <t>Sounds/PlantsSound/Pumpkin_Swallowing,Sounds/PlantsSound/Pumpkin_Swallowing_2</t>
+  </si>
+  <si>
+    <t>Billiard_Ball_Collision_2</t>
+  </si>
+  <si>
+    <t>台球碰撞（土豆碰撞）</t>
+  </si>
+  <si>
+    <t>Sounds/PlantsSound/Billiard_Ball_Collision_2</t>
+  </si>
+  <si>
+    <t>Billiard_Ball_Pocketing_Sound</t>
+  </si>
+  <si>
+    <t>台球落袋声音</t>
+  </si>
+  <si>
+    <t>Sounds/PlantsSound/Billiard_Ball_Pocketing_Sound</t>
+  </si>
+  <si>
+    <t>Potato_Splitting</t>
+  </si>
+  <si>
+    <t>土豆分裂</t>
+  </si>
+  <si>
+    <t>Sounds/PlantsSound/Potato_Splitting</t>
+  </si>
+  <si>
+    <t>Giant_Crop_Falling_to_Ground</t>
+  </si>
+  <si>
+    <t>巨大作物落地</t>
+  </si>
+  <si>
+    <t>Sounds/PlantsSound/Giant_Crop_Falling_to_Ground</t>
+  </si>
+  <si>
+    <t>Harvesting_Strange_Crop_2</t>
+  </si>
+  <si>
+    <t>收获奇异作物（花椰菜羊出现时）</t>
+  </si>
+  <si>
+    <t>Sounds/PlantsSound/Harvesting_Strange_Crop_2</t>
+  </si>
+  <si>
+    <t>Harvesting_Regular_Crop</t>
+  </si>
+  <si>
+    <t>收获普通作物</t>
+  </si>
+  <si>
+    <t>Sounds/PlantsSound/Harvesting_Regular_Crop</t>
+  </si>
+  <si>
+    <t>Water_Beet_Falling_to_Ground</t>
+  </si>
+  <si>
+    <t>水甜菜落地</t>
+  </si>
+  <si>
+    <t>Sounds/PlantsSound/Water_Beet_Falling_to_Ground</t>
+  </si>
+  <si>
+    <t>Bush_Swaying</t>
+  </si>
+  <si>
+    <t>灌木丛晃动（grass碰撞）</t>
+  </si>
+  <si>
+    <t>Sounds/PlantsSound/Bush_Swaying</t>
+  </si>
+  <si>
+    <t>Item_Falling_into_Water_Sound</t>
+  </si>
+  <si>
+    <t>物品落水声</t>
+  </si>
+  <si>
+    <t>Sounds/PlantsSound/Item_Falling_into_Water_Sound</t>
+  </si>
+  <si>
+    <t>Character_Discarding_Item</t>
+  </si>
+  <si>
+    <t>人物丢弃物品</t>
+  </si>
+  <si>
+    <t>Sounds/RoleSound/Character_Discarding_Item</t>
+  </si>
+  <si>
+    <t>Character_Lifting_Item</t>
+  </si>
+  <si>
+    <t>人物举起物品</t>
+  </si>
+  <si>
+    <t>Sounds/RoleSound/Character_Lifting_Item</t>
+  </si>
+  <si>
+    <t>Character_Landing_after_Falling_from_Sky</t>
+  </si>
+  <si>
+    <t>人物从天而降后的落地声</t>
+  </si>
+  <si>
+    <t>Sounds/RoleSound/Character_Landing_after_Falling_from_Sky</t>
+  </si>
+  <si>
+    <t>Character_Eating_Food_1</t>
+  </si>
+  <si>
+    <t>人物吃下食物</t>
+  </si>
+  <si>
+    <t>Sounds/RoleSound/Character_Eating_Food_1,Sounds/RoleSound/Character_Eating_Food_2</t>
+  </si>
+  <si>
+    <t>Character_Picking_up_Item</t>
+  </si>
+  <si>
+    <t>人物拾取物品</t>
+  </si>
+  <si>
+    <t>Sounds/RoleSound/Character_Picking_up_Item</t>
+  </si>
+  <si>
+    <t>Character_Walking_Wooden_Bridge_1</t>
+  </si>
+  <si>
+    <t>人物走路-木桥（木桥碰撞）</t>
+  </si>
+  <si>
+    <t>Sounds/RoleSound/Character_Walking_Wooden_Bridge_1,Sounds/RoleSound/Character_Walking_Wooden_Bridge_2,Sounds/RoleSound/Character_Walking_Wooden_Bridge_3,Sounds/RoleSound/Character_Walking_Wooden_Bridge_4,Sounds/RoleSound/Character_Walking_Wooden_Bridge_5</t>
+  </si>
+  <si>
+    <t>Character_Walking_Sand_Soil</t>
+  </si>
+  <si>
+    <t>人物走路-沙土</t>
+  </si>
+  <si>
+    <t>Sounds/RoleSound/Character_Walking_Sand_Soil,Sounds/RoleSound/Character_Walking_Sand_Soil_2,Sounds/RoleSound/Character_Walking_Sand_Soil_3,Sounds/RoleSound/Character_Walking_Sand_Soil_4,Sounds/RoleSound/Character_Walking_Sand_Soil_5</t>
+  </si>
+  <si>
+    <t>Character_Walking_Beach</t>
+  </si>
+  <si>
+    <t>人物走路-沙滩（看情况，可以不做）</t>
+  </si>
+  <si>
+    <t>Sounds/RoleSound/Character_Walking_Beach,Sounds/RoleSound/Character_Walking_Beach_4,Sounds/RoleSound/Character_Walking_Beach_5</t>
+  </si>
+  <si>
+    <t>Character_Walking_Lotus_Leaf_Path</t>
+  </si>
+  <si>
+    <t>人物走路-荷叶路（荷叶碰撞）</t>
+  </si>
+  <si>
+    <t>Sounds/RoleSound/Character_Walking_Lotus_Leaf_Path,Sounds/RoleSound/Character_Walking_Lotus_Leaf_Path_2</t>
+  </si>
+  <si>
+    <t>Character_Walking_Default</t>
+  </si>
+  <si>
+    <t>人物走路-默认</t>
+  </si>
+  <si>
+    <t>Sounds/RoleSound/Character_Walking_Default，Sounds/RoleSound/Character_Walking_Default_2</t>
+  </si>
+  <si>
+    <t>Eat_Popcorn</t>
+  </si>
+  <si>
+    <t>吃爆米花</t>
+  </si>
+  <si>
+    <t>Sounds/RoleSound/Eat_Popcorn</t>
+  </si>
+  <si>
+    <t>Button_Click</t>
+  </si>
+  <si>
+    <t>点击按钮</t>
+  </si>
+  <si>
+    <t>Sounds/UISound/Button_Click</t>
+  </si>
+  <si>
+    <t>Mouse_Focus_1</t>
+  </si>
+  <si>
+    <t>鼠标按钮聚焦</t>
+  </si>
+  <si>
+    <t>Sounds/UISound/Mouse_Focus_1,Sounds/UISound/Mouse_Focus_2</t>
+  </si>
+  <si>
     <t>Sheep_Bleat</t>
   </si>
   <si>
-    <t>Sounds/NPCSound/Sheep_Bleat_1,Sounds/NPCSound/Sheep_Bleat_2,Sounds/NPCSound/Sheep_Bleat_3,Sounds/NPCSound/Sheep_Bleat_4</t>
-  </si>
-  <si>
-    <t>Q_Bouncy_Crop_1</t>
-  </si>
-  <si>
-    <t>q弹作物1（蘑菇碰撞时）</t>
-  </si>
-  <si>
     <t>Q_Bouncy_Crop</t>
   </si>
   <si>
-    <t>Sounds/PlantsSound/Q_Bouncy_Crop_1,Sounds/PlantsSound/Q_Bouncy_Crop_2,Sounds/PlantsSound/Q_Bouncy_Crop_3</t>
-  </si>
-  <si>
-    <t>Character_Planting_Plant</t>
-  </si>
-  <si>
-    <t>人物种下植物</t>
-  </si>
-  <si>
-    <t>Sounds/PlantsSound/Character_Planting_Plant</t>
-  </si>
-  <si>
-    <t>Crop_Falling_to_Ground</t>
-  </si>
-  <si>
-    <t>作物落地</t>
-  </si>
-  <si>
-    <t>Sounds/PlantsSound/Crop_Falling_to_Ground</t>
-  </si>
-  <si>
-    <t>Bowling_Pin_Falling_Sound</t>
-  </si>
-  <si>
-    <t>保龄球倒地声音（胡萝卜被碰）</t>
-  </si>
-  <si>
-    <t>Sounds/PlantsSound/Bowling_Pin_Falling_Sound</t>
-  </si>
-  <si>
-    <t>Bowling_Ball_Rolling_Sound</t>
-  </si>
-  <si>
-    <t>保龄球滚动声音（猕猴桃状态玩家移动）</t>
-  </si>
-  <si>
-    <t>Sounds/PlantsSound/Bowling_Ball_Rolling_Sound</t>
-  </si>
-  <si>
-    <t>Bowling_Ball_Collision_Sound</t>
-  </si>
-  <si>
-    <t>保龄球碰撞声音（猕猴桃碰撞）</t>
-  </si>
-  <si>
-    <t>Sounds/PlantsSound/Bowling_Ball_Collision_Sound</t>
-  </si>
-  <si>
-    <t>Pumpkin_Swallowing</t>
-  </si>
-  <si>
-    <t>南瓜吞咽</t>
-  </si>
-  <si>
-    <t>Sounds/PlantsSound/Pumpkin_Swallowing,Sounds/PlantsSound/Pumpkin_Swallowing_2</t>
-  </si>
-  <si>
-    <t>Billiard_Ball_Collision_2</t>
-  </si>
-  <si>
-    <t>台球碰撞（土豆碰撞）</t>
-  </si>
-  <si>
-    <t>Sounds/PlantsSound/Billiard_Ball_Collision_2</t>
-  </si>
-  <si>
-    <t>Billiard_Ball_Pocketing_Sound</t>
-  </si>
-  <si>
-    <t>台球落袋声音</t>
-  </si>
-  <si>
-    <t>Sounds/PlantsSound/Billiard_Ball_Pocketing_Sound</t>
-  </si>
-  <si>
-    <t>Potato_Splitting</t>
-  </si>
-  <si>
-    <t>土豆分裂</t>
-  </si>
-  <si>
-    <t>Sounds/PlantsSound/Potato_Splitting</t>
-  </si>
-  <si>
-    <t>Giant_Crop_Falling_to_Ground</t>
-  </si>
-  <si>
-    <t>巨大作物落地</t>
-  </si>
-  <si>
-    <t>Sounds/PlantsSound/Giant_Crop_Falling_to_Ground</t>
-  </si>
-  <si>
-    <t>Harvesting_Strange_Crop_2</t>
-  </si>
-  <si>
-    <t>收获奇异作物（花椰菜羊出现时）</t>
-  </si>
-  <si>
-    <t>Sounds/PlantsSound/Harvesting_Strange_Crop_2</t>
-  </si>
-  <si>
-    <t>Harvesting_Regular_Crop</t>
-  </si>
-  <si>
-    <t>收获普通作物</t>
-  </si>
-  <si>
-    <t>Sounds/PlantsSound/Harvesting_Regular_Crop</t>
-  </si>
-  <si>
-    <t>Water_Beet_Falling_to_Ground</t>
-  </si>
-  <si>
-    <t>水甜菜落地</t>
-  </si>
-  <si>
-    <t>Sounds/PlantsSound/Water_Beet_Falling_to_Ground</t>
-  </si>
-  <si>
-    <t>Bush_Swaying</t>
-  </si>
-  <si>
-    <t>灌木丛晃动（grass碰撞）</t>
-  </si>
-  <si>
-    <t>Sounds/PlantsSound/Bush_Swaying</t>
-  </si>
-  <si>
-    <t>Item_Falling_into_Water_Sound</t>
-  </si>
-  <si>
-    <t>物品落水声</t>
-  </si>
-  <si>
-    <t>Sounds/PlantsSound/Item_Falling_into_Water_Sound</t>
-  </si>
-  <si>
-    <t>Character_Discarding_Item</t>
-  </si>
-  <si>
-    <t>人物丢弃物品</t>
-  </si>
-  <si>
-    <t>Sounds/RoleSound/Character_Discarding_Item</t>
-  </si>
-  <si>
-    <t>Character_Lifting_Item</t>
-  </si>
-  <si>
-    <t>人物举起物品</t>
-  </si>
-  <si>
-    <t>Sounds/RoleSound/Character_Lifting_Item</t>
-  </si>
-  <si>
-    <t>Character_Landing_after_Falling_from_Sky</t>
-  </si>
-  <si>
-    <t>人物从天而降后的落地声</t>
-  </si>
-  <si>
-    <t>Sounds/RoleSound/Character_Landing_after_Falling_from_Sky</t>
-  </si>
-  <si>
-    <t>Character_Eating_Food_1</t>
-  </si>
-  <si>
-    <t>人物吃下食物</t>
-  </si>
-  <si>
     <t>Character_Eating_Food</t>
   </si>
   <si>
-    <t>Sounds/RoleSound/Character_Eating_Food_1,Sounds/RoleSound/Character_Eating_Food_2</t>
-  </si>
-  <si>
-    <t>Character_Picking_up_Item</t>
-  </si>
-  <si>
-    <t>人物拾取物品</t>
-  </si>
-  <si>
-    <t>Sounds/RoleSound/Character_Picking_up_Item</t>
-  </si>
-  <si>
-    <t>Character_Walking_Wooden_Bridge_1</t>
-  </si>
-  <si>
-    <t>人物走路-木桥（木桥碰撞）</t>
-  </si>
-  <si>
     <t>Character_Walking_Wooden_Bridge</t>
   </si>
   <si>
-    <t>Sounds/RoleSound/Character_Walking_Wooden_Bridge_1,Sounds/RoleSound/Character_Walking_Wooden_Bridge_2,Sounds/RoleSound/Character_Walking_Wooden_Bridge_3,Sounds/RoleSound/Character_Walking_Wooden_Bridge_4,Sounds/RoleSound/Character_Walking_Wooden_Bridge_5</t>
-  </si>
-  <si>
-    <t>Character_Walking_Sand_Soil</t>
-  </si>
-  <si>
-    <t>人物走路-沙土</t>
-  </si>
-  <si>
-    <t>Sounds/RoleSound/Character_Walking_Sand_Soil,Sounds/RoleSound/Character_Walking_Sand_Soil_2,Sounds/RoleSound/Character_Walking_Sand_Soil_3,Sounds/RoleSound/Character_Walking_Sand_Soil_4,Sounds/RoleSound/Character_Walking_Sand_Soil_5</t>
-  </si>
-  <si>
-    <t>Character_Walking_Beach</t>
-  </si>
-  <si>
-    <t>人物走路-沙滩（看情况，可以不做）</t>
-  </si>
-  <si>
-    <t>Sounds/RoleSound/Character_Walking_Beach,Sounds/RoleSound/Character_Walking_Beach_4,Sounds/RoleSound/Character_Walking_Beach_5</t>
-  </si>
-  <si>
-    <t>Character_Walking_Lotus_Leaf_Path</t>
-  </si>
-  <si>
-    <t>人物走路-荷叶路（荷叶碰撞）</t>
-  </si>
-  <si>
-    <t>Sounds/RoleSound/Character_Walking_Lotus_Leaf_Path,Sounds/RoleSound/Character_Walking_Lotus_Leaf_Path_2</t>
-  </si>
-  <si>
-    <t>Character_Walking_Default</t>
-  </si>
-  <si>
-    <t>人物走路-默认</t>
-  </si>
-  <si>
-    <t>Sounds/RoleSound/Character_Walking_Default，Sounds/RoleSound/Character_Walking_Default_2</t>
-  </si>
-  <si>
-    <t>Eat_Popcorn</t>
-  </si>
-  <si>
-    <t>吃爆米花</t>
-  </si>
-  <si>
-    <t>Sounds/RoleSound/Eat_Popcorn</t>
-  </si>
-  <si>
-    <t>Button_Click</t>
-  </si>
-  <si>
-    <t>点击按钮</t>
-  </si>
-  <si>
-    <t>Sounds/UISound/Button_Click</t>
-  </si>
-  <si>
-    <t>Mouse_Focus_1</t>
-  </si>
-  <si>
-    <t>鼠标按钮聚焦</t>
-  </si>
-  <si>
     <t>Mouse_Focus</t>
-  </si>
-  <si>
-    <t>Sounds/UISound/Mouse_Focus_1,Sounds/UISound/Mouse_Focus_2</t>
   </si>
 </sst>
 </file>
@@ -1731,7 +1734,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
@@ -1779,47 +1782,47 @@
         <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="2:6">
@@ -1827,16 +1830,16 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="2:6">
@@ -1844,16 +1847,16 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="2:6">
@@ -1861,16 +1864,16 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="2:6">
@@ -1878,16 +1881,16 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" t="s">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="2:6">
@@ -1895,16 +1898,16 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="2:6">
@@ -1912,16 +1915,16 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="E10">
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="2:6">
@@ -1929,16 +1932,16 @@
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="E11">
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="2:6">
@@ -1946,16 +1949,16 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" t="s">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="E12">
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="2:6">
@@ -1963,16 +1966,16 @@
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" t="s">
-        <v>43</v>
+        <v>45</v>
+      </c>
+      <c r="E13">
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="2:6">
@@ -1980,16 +1983,16 @@
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
-      </c>
-      <c r="E14" t="s">
-        <v>46</v>
+        <v>48</v>
+      </c>
+      <c r="E14">
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="2:6">
@@ -1997,13 +2000,13 @@
         <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15" t="s">
         <v>51</v>
+      </c>
+      <c r="E15">
+        <v>11</v>
       </c>
       <c r="F15" t="s">
         <v>52</v>
@@ -2019,11 +2022,11 @@
       <c r="D16" t="s">
         <v>54</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
         <v>55</v>
-      </c>
-      <c r="F16" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="17" spans="2:6">
@@ -2031,16 +2034,16 @@
         <v>13</v>
       </c>
       <c r="C17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" t="s">
         <v>57</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17">
+        <v>13</v>
+      </c>
+      <c r="F17" t="s">
         <v>58</v>
-      </c>
-      <c r="E17" t="s">
-        <v>57</v>
-      </c>
-      <c r="F17" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -2048,16 +2051,16 @@
         <v>14</v>
       </c>
       <c r="C18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" t="s">
         <v>60</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18">
+        <v>14</v>
+      </c>
+      <c r="F18" t="s">
         <v>61</v>
-      </c>
-      <c r="E18" t="s">
-        <v>60</v>
-      </c>
-      <c r="F18" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="19" spans="2:6">
@@ -2065,16 +2068,16 @@
         <v>15</v>
       </c>
       <c r="C19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" t="s">
         <v>63</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19">
+        <v>15</v>
+      </c>
+      <c r="F19" t="s">
         <v>64</v>
-      </c>
-      <c r="E19" t="s">
-        <v>63</v>
-      </c>
-      <c r="F19" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="20" spans="2:6">
@@ -2082,16 +2085,16 @@
         <v>16</v>
       </c>
       <c r="C20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="E20">
+        <v>16</v>
+      </c>
+      <c r="F20" t="s">
         <v>67</v>
-      </c>
-      <c r="E20" t="s">
-        <v>66</v>
-      </c>
-      <c r="F20" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="21" spans="2:6">
@@ -2099,16 +2102,16 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" t="s">
         <v>69</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21">
+        <v>17</v>
+      </c>
+      <c r="F21" t="s">
         <v>70</v>
-      </c>
-      <c r="E21" t="s">
-        <v>69</v>
-      </c>
-      <c r="F21" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -2116,16 +2119,16 @@
         <v>18</v>
       </c>
       <c r="C22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" t="s">
         <v>72</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22">
+        <v>18</v>
+      </c>
+      <c r="F22" t="s">
         <v>73</v>
-      </c>
-      <c r="E22" t="s">
-        <v>72</v>
-      </c>
-      <c r="F22" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="23" spans="2:6">
@@ -2133,16 +2136,16 @@
         <v>19</v>
       </c>
       <c r="C23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" t="s">
         <v>75</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23">
+        <v>19</v>
+      </c>
+      <c r="F23" t="s">
         <v>76</v>
-      </c>
-      <c r="E23" t="s">
-        <v>75</v>
-      </c>
-      <c r="F23" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="24" spans="2:6">
@@ -2150,16 +2153,16 @@
         <v>20</v>
       </c>
       <c r="C24" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="E24">
+        <v>20</v>
+      </c>
+      <c r="F24" t="s">
         <v>79</v>
-      </c>
-      <c r="E24" t="s">
-        <v>78</v>
-      </c>
-      <c r="F24" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="25" spans="2:6">
@@ -2167,16 +2170,16 @@
         <v>21</v>
       </c>
       <c r="C25" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" t="s">
         <v>81</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25">
+        <v>21</v>
+      </c>
+      <c r="F25" t="s">
         <v>82</v>
-      </c>
-      <c r="E25" t="s">
-        <v>81</v>
-      </c>
-      <c r="F25" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="26" spans="2:6">
@@ -2184,16 +2187,16 @@
         <v>22</v>
       </c>
       <c r="C26" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" t="s">
         <v>84</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26">
+        <v>22</v>
+      </c>
+      <c r="F26" t="s">
         <v>85</v>
-      </c>
-      <c r="E26" t="s">
-        <v>84</v>
-      </c>
-      <c r="F26" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -2201,16 +2204,16 @@
         <v>23</v>
       </c>
       <c r="C27" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" t="s">
         <v>87</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27">
+        <v>23</v>
+      </c>
+      <c r="F27" t="s">
         <v>88</v>
-      </c>
-      <c r="E27" t="s">
-        <v>87</v>
-      </c>
-      <c r="F27" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="28" spans="2:6">
@@ -2218,16 +2221,16 @@
         <v>24</v>
       </c>
       <c r="C28" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" t="s">
         <v>90</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28">
+        <v>24</v>
+      </c>
+      <c r="F28" t="s">
         <v>91</v>
-      </c>
-      <c r="E28" t="s">
-        <v>90</v>
-      </c>
-      <c r="F28" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="29" spans="2:6">
@@ -2235,16 +2238,16 @@
         <v>25</v>
       </c>
       <c r="C29" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" t="s">
         <v>93</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29">
+        <v>25</v>
+      </c>
+      <c r="F29" t="s">
         <v>94</v>
-      </c>
-      <c r="E29" t="s">
-        <v>93</v>
-      </c>
-      <c r="F29" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -2252,16 +2255,16 @@
         <v>26</v>
       </c>
       <c r="C30" t="s">
+        <v>95</v>
+      </c>
+      <c r="D30" t="s">
         <v>96</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30">
+        <v>26</v>
+      </c>
+      <c r="F30" t="s">
         <v>97</v>
-      </c>
-      <c r="E30" t="s">
-        <v>96</v>
-      </c>
-      <c r="F30" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -2269,16 +2272,16 @@
         <v>27</v>
       </c>
       <c r="C31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D31" t="s">
         <v>99</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31">
+        <v>27</v>
+      </c>
+      <c r="F31" t="s">
         <v>100</v>
-      </c>
-      <c r="E31" t="s">
-        <v>99</v>
-      </c>
-      <c r="F31" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="32" spans="2:6">
@@ -2286,16 +2289,16 @@
         <v>28</v>
       </c>
       <c r="C32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D32" t="s">
         <v>102</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32">
+        <v>28</v>
+      </c>
+      <c r="F32" t="s">
         <v>103</v>
-      </c>
-      <c r="E32" t="s">
-        <v>102</v>
-      </c>
-      <c r="F32" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="33" spans="2:6">
@@ -2303,16 +2306,16 @@
         <v>29</v>
       </c>
       <c r="C33" t="s">
+        <v>104</v>
+      </c>
+      <c r="D33" t="s">
         <v>105</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33">
+        <v>29</v>
+      </c>
+      <c r="F33" t="s">
         <v>106</v>
-      </c>
-      <c r="E33" t="s">
-        <v>105</v>
-      </c>
-      <c r="F33" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="34" spans="2:6">
@@ -2320,16 +2323,16 @@
         <v>30</v>
       </c>
       <c r="C34" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" t="s">
         <v>108</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34">
+        <v>30</v>
+      </c>
+      <c r="F34" t="s">
         <v>109</v>
-      </c>
-      <c r="E34" t="s">
-        <v>108</v>
-      </c>
-      <c r="F34" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="35" spans="2:6">
@@ -2337,16 +2340,16 @@
         <v>31</v>
       </c>
       <c r="C35" t="s">
+        <v>110</v>
+      </c>
+      <c r="D35" t="s">
         <v>111</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35">
+        <v>31</v>
+      </c>
+      <c r="F35" t="s">
         <v>112</v>
-      </c>
-      <c r="E35" t="s">
-        <v>113</v>
-      </c>
-      <c r="F35" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="36" spans="2:6">
@@ -2354,16 +2357,16 @@
         <v>32</v>
       </c>
       <c r="C36" t="s">
+        <v>113</v>
+      </c>
+      <c r="D36" t="s">
+        <v>114</v>
+      </c>
+      <c r="E36">
+        <v>32</v>
+      </c>
+      <c r="F36" t="s">
         <v>115</v>
-      </c>
-      <c r="D36" t="s">
-        <v>116</v>
-      </c>
-      <c r="E36" t="s">
-        <v>115</v>
-      </c>
-      <c r="F36" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="37" spans="2:6">
@@ -2371,16 +2374,16 @@
         <v>33</v>
       </c>
       <c r="C37" t="s">
+        <v>116</v>
+      </c>
+      <c r="D37" t="s">
+        <v>117</v>
+      </c>
+      <c r="E37">
+        <v>33</v>
+      </c>
+      <c r="F37" t="s">
         <v>118</v>
-      </c>
-      <c r="D37" t="s">
-        <v>119</v>
-      </c>
-      <c r="E37" t="s">
-        <v>120</v>
-      </c>
-      <c r="F37" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="38" spans="2:6">
@@ -2388,16 +2391,16 @@
         <v>34</v>
       </c>
       <c r="C38" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E38" t="s">
-        <v>122</v>
+        <v>120</v>
+      </c>
+      <c r="E38">
+        <v>34</v>
       </c>
       <c r="F38" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="2:6">
@@ -2405,16 +2408,16 @@
         <v>35</v>
       </c>
       <c r="C39" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D39" t="s">
-        <v>126</v>
-      </c>
-      <c r="E39" t="s">
-        <v>125</v>
+        <v>123</v>
+      </c>
+      <c r="E39">
+        <v>35</v>
       </c>
       <c r="F39" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="2:6">
@@ -2422,16 +2425,16 @@
         <v>36</v>
       </c>
       <c r="C40" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D40" t="s">
-        <v>129</v>
-      </c>
-      <c r="E40" t="s">
-        <v>128</v>
+        <v>126</v>
+      </c>
+      <c r="E40">
+        <v>36</v>
       </c>
       <c r="F40" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="2:6">
@@ -2439,16 +2442,16 @@
         <v>37</v>
       </c>
       <c r="C41" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D41" t="s">
-        <v>132</v>
-      </c>
-      <c r="E41" t="s">
-        <v>131</v>
+        <v>129</v>
+      </c>
+      <c r="E41">
+        <v>37</v>
       </c>
       <c r="F41" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="42" spans="2:6">
@@ -2456,16 +2459,16 @@
         <v>38</v>
       </c>
       <c r="C42" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D42" t="s">
-        <v>135</v>
-      </c>
-      <c r="E42" t="s">
-        <v>134</v>
+        <v>132</v>
+      </c>
+      <c r="E42">
+        <v>38</v>
       </c>
       <c r="F42" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="43" spans="2:6">
@@ -2473,16 +2476,16 @@
         <v>39</v>
       </c>
       <c r="C43" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D43" t="s">
-        <v>138</v>
-      </c>
-      <c r="E43" t="s">
-        <v>137</v>
+        <v>135</v>
+      </c>
+      <c r="E43">
+        <v>39</v>
       </c>
       <c r="F43" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="2:6">
@@ -2490,16 +2493,336 @@
         <v>40</v>
       </c>
       <c r="C44" t="s">
+        <v>137</v>
+      </c>
+      <c r="D44" t="s">
+        <v>138</v>
+      </c>
+      <c r="E44">
+        <v>40</v>
+      </c>
+      <c r="F44" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>10</v>
+      </c>
+      <c r="B49" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>10</v>
+      </c>
+      <c r="B50" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>10</v>
+      </c>
+      <c r="B51" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>10</v>
+      </c>
+      <c r="B52" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>10</v>
+      </c>
+      <c r="B53" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>10</v>
+      </c>
+      <c r="B54" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>10</v>
+      </c>
+      <c r="B55" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>10</v>
+      </c>
+      <c r="B56" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>10</v>
+      </c>
+      <c r="B57" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>10</v>
+      </c>
+      <c r="B58" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>10</v>
+      </c>
+      <c r="B59" t="s">
         <v>140</v>
       </c>
-      <c r="D44" t="s">
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>10</v>
+      </c>
+      <c r="B60" t="s">
         <v>141</v>
       </c>
-      <c r="E44" t="s">
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>10</v>
+      </c>
+      <c r="B61" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>10</v>
+      </c>
+      <c r="B62" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>10</v>
+      </c>
+      <c r="B63" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>10</v>
+      </c>
+      <c r="B64" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>10</v>
+      </c>
+      <c r="B65" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" t="s">
+        <v>10</v>
+      </c>
+      <c r="B66" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" t="s">
+        <v>10</v>
+      </c>
+      <c r="B67" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>10</v>
+      </c>
+      <c r="B68" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>10</v>
+      </c>
+      <c r="B69" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>10</v>
+      </c>
+      <c r="B70" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>10</v>
+      </c>
+      <c r="B71" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>10</v>
+      </c>
+      <c r="B72" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>10</v>
+      </c>
+      <c r="B73" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>10</v>
+      </c>
+      <c r="B74" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>10</v>
+      </c>
+      <c r="B75" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>10</v>
+      </c>
+      <c r="B76" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>10</v>
+      </c>
+      <c r="B77" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>10</v>
+      </c>
+      <c r="B78" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>10</v>
+      </c>
+      <c r="B79" t="s">
         <v>142</v>
       </c>
-      <c r="F44" t="s">
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>10</v>
+      </c>
+      <c r="B80" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>10</v>
+      </c>
+      <c r="B81" t="s">
         <v>143</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>10</v>
+      </c>
+      <c r="B82" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
+        <v>10</v>
+      </c>
+      <c r="B83" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" t="s">
+        <v>10</v>
+      </c>
+      <c r="B84" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>10</v>
+      </c>
+      <c r="B85" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>10</v>
+      </c>
+      <c r="B86" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" t="s">
+        <v>10</v>
+      </c>
+      <c r="B87" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" t="s">
+        <v>10</v>
+      </c>
+      <c r="B88" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/Tools/Luban/DataTables/Datas/Y_音效.xlsx
+++ b/Tools/Luban/DataTables/Datas/Y_音效.xlsx
@@ -83,7 +83,7 @@
     <t>中文描述</t>
   </si>
   <si>
-    <t>合适触发，枚举</t>
+    <t>合适触发,枚举</t>
   </si>
   <si>
     <t>path1,path2</t>
@@ -398,7 +398,7 @@
     <t>Character_Walking_Beach</t>
   </si>
   <si>
-    <t>人物走路-沙滩（看情况，可以不做）</t>
+    <t>人物走路-沙滩（看情况,可以不做）</t>
   </si>
   <si>
     <t>Sounds/RoleSound/Character_Walking_Beach,Sounds/RoleSound/Character_Walking_Beach_4,Sounds/RoleSound/Character_Walking_Beach_5</t>
@@ -419,7 +419,7 @@
     <t>人物走路-默认</t>
   </si>
   <si>
-    <t>Sounds/RoleSound/Character_Walking_Default，Sounds/RoleSound/Character_Walking_Default_2</t>
+    <t>Sounds/RoleSound/Character_Walking_Default,Sounds/RoleSound/Character_Walking_Default_2</t>
   </si>
   <si>
     <t>Eat_Popcorn</t>
